--- a/skills/stock-etf-analysis/assets/example/BBS_Valuation_Model_NVDA_META.xlsx
+++ b/skills/stock-etf-analysis/assets/example/BBS_Valuation_Model_NVDA_META.xlsx
@@ -805,7 +805,7 @@
     <t xml:space="preserve">Brand-to-Balance-Sheet (BBS) valuation model: NVIDIA and Meta Platforms</t>
   </si>
   <si>
-    <t xml:space="preserve">Brand-to-Balance-Sheet (BBS) method by Jay Nair · github.com/jay-nair-builds/toolkit</t>
+    <t xml:space="preserve">Brand-to-Balance-Sheet (BBS) method by Jay Nair · github.com/jay-nair-builds/foundry</t>
   </si>
   <si>
     <t xml:space="preserve">Prices at close on 18 Sep 2026, USD billions unless stated. Education only: not personalised investment advice and not a recommendation to buy, sell or hold.</t>
